--- a/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
+++ b/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1558996280450782</v>
+        <v>-0.1558996280450781</v>
       </c>
     </row>
     <row r="6">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7128634150487455</v>
+        <v>0.7128634150487454</v>
       </c>
     </row>
     <row r="12">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.307097450092551</v>
+        <v>1.30709745009255</v>
       </c>
     </row>
     <row r="14">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2738711846265848</v>
+        <v>0.2738711846265844</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,20 +621,25 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>EXPERIMENTAL_SET</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>IDH1_STATUS</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>RNA_AVAILABLE</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>BENEFIT_BINARY</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>RS_Z</t>
         </is>
@@ -647,13 +652,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6741225709545156</v>
+        <v>0.6741225709545154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3705533249609645</v>
+        <v>0.3705533249609646</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3035692459935511</v>
+        <v>0.3035692459935508</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -682,17 +687,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.890327821111403</v>
+      <c r="N2" t="n">
+        <v>1.890327821111402</v>
       </c>
     </row>
     <row r="3">
@@ -705,10 +715,10 @@
         <v>0.3118390881364234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.402374055434859</v>
+        <v>0.4023740554348589</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -737,17 +747,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1536022691023406</v>
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1536022691023411</v>
       </c>
     </row>
     <row r="4">
@@ -792,16 +807,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.5497555026933404</v>
       </c>
     </row>
@@ -815,7 +835,7 @@
         <v>0.6867618794440014</v>
       </c>
       <c r="C5" t="n">
-        <v>0.337676499616521</v>
+        <v>0.3376764996165211</v>
       </c>
       <c r="D5" t="n">
         <v>0.3490853798274803</v>
@@ -847,16 +867,21 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2.090906830398682</v>
       </c>
     </row>
@@ -902,17 +927,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
-        <v>-0.5669879424213801</v>
+      <c r="N6" t="n">
+        <v>-0.5669879424213802</v>
       </c>
     </row>
     <row r="7">
@@ -928,7 +958,7 @@
         <v>0.5864783189261368</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.325687326512341</v>
+        <v>-0.3256873265123409</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -957,17 +987,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>-0.8826594532747007</v>
+      <c r="N7" t="n">
+        <v>-0.8826594532747005</v>
       </c>
     </row>
     <row r="8">
@@ -977,10 +1012,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5951237281573062</v>
+        <v>0.5951237281573063</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4041932886603292</v>
+        <v>0.4041932886603293</v>
       </c>
       <c r="D8" t="n">
         <v>0.190930439496977</v>
@@ -1012,16 +1047,21 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
         <v>1.393954814194397</v>
       </c>
     </row>
@@ -1067,17 +1107,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4443135750350134</v>
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4443135750350135</v>
       </c>
     </row>
     <row r="10">
@@ -1122,16 +1167,21 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1.019099448631347</v>
       </c>
     </row>
@@ -1177,16 +1227,21 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L11" t="b">
         <v>1</v>
       </c>
       <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
         <v>-1.043149928054248</v>
       </c>
     </row>
@@ -1200,10 +1255,10 @@
         <v>0.250863755195081</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6293909101742615</v>
+        <v>0.6293909101742614</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3785271549791805</v>
+        <v>-0.3785271549791804</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1232,17 +1287,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L12" t="b">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.115512280438328</v>
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1.115512280438327</v>
       </c>
     </row>
     <row r="13">
@@ -1255,10 +1315,10 @@
         <v>0.1716451268055921</v>
       </c>
       <c r="C13" t="n">
-        <v>0.672915387130386</v>
+        <v>0.6729153871303859</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5012702603247939</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1287,16 +1347,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-1.656412580909693</v>
       </c>
     </row>
@@ -1342,16 +1407,21 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-1.210261511669543</v>
       </c>
     </row>
@@ -1362,13 +1432,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.381623523649759</v>
+        <v>0.3816235236497591</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5485467523459439</v>
+        <v>0.5485467523459437</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961846</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1397,17 +1467,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>-0.1830230217943296</v>
+      <c r="N15" t="n">
+        <v>-0.1830230217943289</v>
       </c>
     </row>
     <row r="16">
@@ -1417,13 +1492,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2828138579726733</v>
+        <v>0.2828138579726732</v>
       </c>
       <c r="C16" t="n">
         <v>0.4976624590930341</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2148486011203608</v>
+        <v>-0.2148486011203609</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1452,17 +1527,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K16" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L16" t="b">
         <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3942189848705998</v>
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.3942189848706001</v>
       </c>
     </row>
     <row r="17">
@@ -1472,13 +1552,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2145524253023635</v>
+        <v>0.2145524253023634</v>
       </c>
       <c r="C17" t="n">
         <v>0.6001120644611281</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3855596391587646</v>
+        <v>-0.3855596391587647</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1507,17 +1587,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
-        <v>-1.14650280161739</v>
+      <c r="N17" t="n">
+        <v>-1.146502801617391</v>
       </c>
     </row>
     <row r="18">
@@ -1527,13 +1612,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4296518046208667</v>
+        <v>0.4296518046208666</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4945453559326178</v>
+        <v>0.4945453559326177</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06489355131175112</v>
+        <v>-0.06489355131175117</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1562,17 +1647,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>0.2665980220829754</v>
+      <c r="N18" t="n">
+        <v>0.2665980220829752</v>
       </c>
     </row>
     <row r="19">
@@ -1617,17 +1707,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>0.7903590860383858</v>
+      <c r="N19" t="n">
+        <v>0.7903590860383859</v>
       </c>
     </row>
     <row r="20">
@@ -1640,10 +1735,10 @@
         <v>0.3693076732017413</v>
       </c>
       <c r="C20" t="n">
-        <v>0.515004568135498</v>
+        <v>0.5150045681354979</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1672,17 +1767,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
-        <v>-0.08948350869765191</v>
+      <c r="N20" t="n">
+        <v>-0.08948350869765143</v>
       </c>
     </row>
     <row r="21">
@@ -1692,7 +1792,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7118486478275275</v>
+        <v>0.7118486478275274</v>
       </c>
       <c r="C21" t="n">
         <v>0.4260034620050295</v>
@@ -1727,16 +1827,21 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>1.812222012682484</v>
       </c>
     </row>
@@ -1782,16 +1887,21 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>-0.3239940175984092</v>
       </c>
     </row>
@@ -1837,16 +1947,21 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L23" t="b">
         <v>1</v>
       </c>
       <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
         <v>1.396760898597113</v>
       </c>
     </row>
@@ -1857,13 +1972,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2175554342042255</v>
+        <v>0.2175554342042256</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5970724973798153</v>
+        <v>0.5970724973798152</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1892,17 +2007,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.119874575488377</v>
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.119874575488376</v>
       </c>
     </row>
     <row r="25">
@@ -1915,10 +2035,10 @@
         <v>0.547386166559502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4276290460083051</v>
+        <v>0.4276290460083053</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1197571205511969</v>
+        <v>0.1197571205511967</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1947,17 +2067,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="n">
-        <v>1.080310561061668</v>
+      <c r="N25" t="n">
+        <v>1.080310561061667</v>
       </c>
     </row>
     <row r="26">
@@ -1967,13 +2092,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2573693650749999</v>
+        <v>0.257369365075</v>
       </c>
       <c r="C26" t="n">
         <v>0.5837653200597678</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3263959549847679</v>
+        <v>-0.3263959549847678</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2002,17 +2127,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="n">
-        <v>-0.8857822140406026</v>
+      <c r="N26" t="n">
+        <v>-0.8857822140406025</v>
       </c>
     </row>
     <row r="27">
@@ -2025,10 +2155,10 @@
         <v>0.1922848927634011</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5332163798977594</v>
+        <v>0.5332163798977593</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2057,17 +2187,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="M27" t="n">
-        <v>-0.9498369215134704</v>
+      <c r="N27" t="n">
+        <v>-0.9498369215134701</v>
       </c>
     </row>
     <row r="28">
@@ -2112,16 +2247,21 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>1.179995326864448</v>
       </c>
     </row>
@@ -2132,13 +2272,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3727681504267594</v>
+        <v>0.3727681504267595</v>
       </c>
       <c r="C29" t="n">
         <v>0.5189573803652675</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1461892299385081</v>
+        <v>-0.146189229938508</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2167,17 +2307,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="M29" t="n">
-        <v>-0.09165311448734394</v>
+      <c r="N29" t="n">
+        <v>-0.0916531144873437</v>
       </c>
     </row>
     <row r="30">
@@ -2193,7 +2338,7 @@
         <v>0.4250474383301707</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1957735252430408</v>
+        <v>-0.1957735252430409</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2222,17 +2367,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L30" t="b">
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3101595646326613</v>
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.3101595646326616</v>
       </c>
     </row>
     <row r="31">
@@ -2242,7 +2392,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2726179454172195</v>
+        <v>0.2726179454172194</v>
       </c>
       <c r="C31" t="n">
         <v>0.5623898070994021</v>
@@ -2277,17 +2427,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L31" t="b">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7243883580184677</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-0.724388358018468</v>
       </c>
     </row>
     <row r="32">
@@ -2300,7 +2455,7 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4830115777026098</v>
+        <v>0.4830115777026097</v>
       </c>
       <c r="D32" t="n">
         <v>-0.1405419733734229</v>
@@ -2332,17 +2487,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="M32" t="n">
-        <v>-0.06676696903508038</v>
+      <c r="N32" t="n">
+        <v>-0.06676696903508014</v>
       </c>
     </row>
     <row r="33">
@@ -2355,10 +2515,10 @@
         <v>0.3328760832679651</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4307152111273059</v>
+        <v>0.4307152111273058</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934062</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2387,17 +2547,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="M33" t="n">
-        <v>0.1214145333353488</v>
+      <c r="N33" t="n">
+        <v>0.1214145333353493</v>
       </c>
     </row>
     <row r="34">
@@ -2442,16 +2607,21 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K34" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>-1.056496021343738</v>
       </c>
     </row>
@@ -2462,10 +2632,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5394791234243425</v>
+        <v>0.5394791234243426</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3857011247696834</v>
+        <v>0.3857011247696835</v>
       </c>
       <c r="D35" t="n">
         <v>0.1537779986546591</v>
@@ -2497,16 +2667,21 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>1.230232653521748</v>
       </c>
     </row>
@@ -2552,17 +2727,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L36" t="b">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="M36" t="n">
-        <v>-0.7129966652452814</v>
+      <c r="N36" t="n">
+        <v>-0.7129966652452815</v>
       </c>
     </row>
     <row r="37">
@@ -2607,17 +2787,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K37" t="b">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L37" t="b">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="M37" t="n">
-        <v>-0.4845703340344917</v>
+      <c r="N37" t="n">
+        <v>-0.4845703340344918</v>
       </c>
     </row>
     <row r="38">
@@ -2662,17 +2847,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K38" t="b">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L38" t="b">
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5569933730109207</v>
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.5569933730109208</v>
       </c>
     </row>
     <row r="39">
@@ -2682,13 +2872,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4653345520848202</v>
+        <v>0.4653345520848203</v>
       </c>
       <c r="C39" t="n">
         <v>0.4840879159829741</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.01875336389815385</v>
+        <v>-0.0187533638981538</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2717,17 +2907,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K39" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L39" t="b">
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4699270902660449</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.4699270902660452</v>
       </c>
     </row>
     <row r="40">
@@ -2740,10 +2935,10 @@
         <v>0.6175455689522186</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3789088878499818</v>
+        <v>0.3789088878499817</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2386366811022367</v>
+        <v>0.2386366811022368</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2772,16 +2967,21 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K40" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L40" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1.604185118747848</v>
       </c>
     </row>
@@ -2795,10 +2995,10 @@
         <v>0.5620888841745206</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3852882355996785</v>
+        <v>0.3852882355996786</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1768006485748422</v>
+        <v>0.1768006485748421</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2827,16 +3027,21 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K41" t="b">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>1.33168811388679</v>
       </c>
     </row>
@@ -2850,7 +3055,7 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4177957142027763</v>
+        <v>0.4177957142027762</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1253328976907889</v>
@@ -2882,17 +3087,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K42" t="b">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L42" t="b">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0002558880407976535</v>
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.0002558880407978982</v>
       </c>
     </row>
     <row r="43">
@@ -2902,7 +3112,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3383392939535171</v>
+        <v>0.3383392939535172</v>
       </c>
       <c r="C43" t="n">
         <v>0.5106782077019681</v>
@@ -2937,17 +3147,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K43" t="b">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L43" t="b">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="M43" t="n">
-        <v>-0.2068886854809438</v>
+      <c r="N43" t="n">
+        <v>-0.2068886854809436</v>
       </c>
     </row>
     <row r="44">
@@ -2957,13 +3172,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.604162001406453</v>
+        <v>0.6041620014064532</v>
       </c>
       <c r="C44" t="n">
         <v>0.3523044639392301</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2518575374672229</v>
+        <v>0.2518575374672231</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2992,17 +3207,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K44" t="b">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="M44" t="n">
-        <v>1.662446355989434</v>
+      <c r="N44" t="n">
+        <v>1.662446355989435</v>
       </c>
     </row>
     <row r="45">
@@ -3015,10 +3235,10 @@
         <v>0.2921192787540448</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4188101764003093</v>
+        <v>0.4188101764003092</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3047,17 +3267,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K45" t="b">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L45" t="b">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.005728501729108614</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.00572850172910837</v>
       </c>
     </row>
     <row r="46">
@@ -3102,16 +3327,21 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K46" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>-0.1772360437891739</v>
       </c>
     </row>
@@ -3125,10 +3355,10 @@
         <v>0.4809391108788849</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5016886059394927</v>
+        <v>0.5016886059394928</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3157,17 +3387,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K47" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L47" t="b">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4611306047729376</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.4611306047729372</v>
       </c>
     </row>
     <row r="48">
@@ -3180,10 +3415,10 @@
         <v>0.2314292087413117</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5043859448095898</v>
+        <v>0.5043859448095896</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3212,17 +3447,22 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K48" t="b">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L48" t="b">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="M48" t="n">
-        <v>-0.6502880126555679</v>
+      <c r="N48" t="n">
+        <v>-0.6502880126555675</v>
       </c>
     </row>
     <row r="49">
@@ -3267,16 +3507,21 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K49" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L49" t="b">
         <v>1</v>
       </c>
       <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
         <v>-1.444171369427372</v>
       </c>
     </row>
@@ -3322,17 +3567,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K50" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="M50" t="n">
-        <v>-0.6321605150517656</v>
+      <c r="N50" t="n">
+        <v>-0.6321605150517657</v>
       </c>
     </row>
     <row r="51">
@@ -3377,16 +3627,21 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K51" t="b">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L51" t="b">
         <v>1</v>
       </c>
       <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
         <v>-1.492094818603322</v>
       </c>
     </row>
@@ -3432,17 +3687,22 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K52" t="b">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L52" t="b">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.9818298904967256</v>
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-0.9818298904967258</v>
       </c>
     </row>
     <row r="53">
@@ -3487,17 +3747,22 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
-        </is>
-      </c>
-      <c r="K53" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Unknown (Paper: n=9 Mutated, n=43 WT)</t>
+        </is>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
         <v>0</v>
       </c>
-      <c r="M53" t="n">
-        <v>-0.9013512936456987</v>
+      <c r="N53" t="n">
+        <v>-0.9013512936456988</v>
       </c>
     </row>
   </sheetData>

--- a/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
+++ b/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7128634150487454</v>
+        <v>0.7128634150487455</v>
       </c>
     </row>
     <row r="12">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3887806899776127</v>
+        <v>0.3887806899776128</v>
       </c>
     </row>
     <row r="13">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2738711846265844</v>
+        <v>0.2738711846265848</v>
       </c>
     </row>
   </sheetData>
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6741225709545154</v>
+        <v>0.6741225709545156</v>
       </c>
       <c r="C2" t="n">
         <v>0.3705533249609646</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3035692459935508</v>
+        <v>0.303569245993551</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.890327821111402</v>
+        <v>1.890327821111403</v>
       </c>
     </row>
     <row r="3">
@@ -718,7 +718,7 @@
         <v>0.4023740554348589</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1536022691023411</v>
+        <v>0.1536022691023414</v>
       </c>
     </row>
     <row r="4">
@@ -775,10 +775,10 @@
         <v>0.5218386559860035</v>
       </c>
       <c r="C4" t="n">
-        <v>0.522477060015217</v>
+        <v>0.5224770600152169</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5497555026933404</v>
+        <v>0.5497555026933409</v>
       </c>
     </row>
     <row r="5">
@@ -895,10 +895,10 @@
         <v>0.2972134155204859</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5512673902348846</v>
+        <v>0.5512673902348847</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2540539747143987</v>
+        <v>-0.2540539747143988</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5669879424213802</v>
+        <v>-0.566987942421381</v>
       </c>
     </row>
     <row r="7">
@@ -958,7 +958,7 @@
         <v>0.5864783189261368</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3256873265123409</v>
+        <v>-0.325687326512341</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8826594532747005</v>
+        <v>-0.8826594532747009</v>
       </c>
     </row>
     <row r="8">
@@ -1015,10 +1015,10 @@
         <v>0.5951237281573063</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4041932886603293</v>
+        <v>0.4041932886603294</v>
       </c>
       <c r="D8" t="n">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969769</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         <v>0.4417500520544824</v>
       </c>
       <c r="C9" t="n">
-        <v>0.466315729969719</v>
+        <v>0.4663157299697189</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02456567791523656</v>
+        <v>-0.02456567791523645</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4443135750350135</v>
+        <v>0.444313575035014</v>
       </c>
     </row>
     <row r="10">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1869441246967853</v>
+        <v>0.1869441246967854</v>
       </c>
       <c r="C11" t="n">
         <v>0.549050545884553</v>
@@ -1255,10 +1255,10 @@
         <v>0.250863755195081</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6293909101742614</v>
+        <v>0.6293909101742613</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>0.3816235236497591</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5485467523459437</v>
+        <v>0.5485467523459439</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1669232286961846</v>
+        <v>-0.1669232286961848</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1830230217943289</v>
+        <v>-0.1830230217943294</v>
       </c>
     </row>
     <row r="16">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2828138579726732</v>
+        <v>0.2828138579726733</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4976624590930341</v>
+        <v>0.4976624590930342</v>
       </c>
       <c r="D16" t="n">
         <v>-0.2148486011203609</v>
@@ -1542,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3942189848706001</v>
+        <v>-0.3942189848706004</v>
       </c>
     </row>
     <row r="17">
@@ -1555,10 +1555,10 @@
         <v>0.2145524253023634</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6001120644611281</v>
+        <v>0.600112064461128</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3855596391587647</v>
+        <v>-0.3855596391587646</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.146502801617391</v>
+        <v>-1.14650280161739</v>
       </c>
     </row>
     <row r="18">
@@ -1735,10 +1735,10 @@
         <v>0.3693076732017413</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5150045681354979</v>
+        <v>0.515004568135498</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08948350869765143</v>
+        <v>-0.08948350869765193</v>
       </c>
     </row>
     <row r="21">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7118486478275274</v>
+        <v>0.7118486478275275</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4260034620050295</v>
+        <v>0.4260034620050296</v>
       </c>
       <c r="D21" t="n">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224979</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>0.4105420803197389</v>
       </c>
       <c r="D23" t="n">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927821</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2175554342042256</v>
+        <v>0.2175554342042255</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5970724973798152</v>
+        <v>0.5970724973798153</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755898</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.119874575488376</v>
+        <v>-1.119874575488377</v>
       </c>
     </row>
     <row r="25">
@@ -2035,10 +2035,10 @@
         <v>0.547386166559502</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4276290460083053</v>
+        <v>0.4276290460083051</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1197571205511967</v>
+        <v>0.1197571205511969</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.080310561061667</v>
+        <v>1.080310561061668</v>
       </c>
     </row>
     <row r="26">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.257369365075</v>
+        <v>0.2573693650749999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5837653200597678</v>
+        <v>0.5837653200597677</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3263959549847678</v>
@@ -2395,10 +2395,10 @@
         <v>0.2726179454172194</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5623898070994021</v>
+        <v>0.562389807099402</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821826</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.724388358018468</v>
+        <v>-0.7243883580184676</v>
       </c>
     </row>
     <row r="32">
@@ -2455,10 +2455,10 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4830115777026097</v>
+        <v>0.4830115777026099</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.06676696903508014</v>
+        <v>-0.06676696903508088</v>
       </c>
     </row>
     <row r="33">
@@ -2515,10 +2515,10 @@
         <v>0.3328760832679651</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4307152111273058</v>
+        <v>0.4307152111273059</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.09783912785934062</v>
+        <v>-0.09783912785934074</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1214145333353493</v>
+        <v>0.1214145333353489</v>
       </c>
     </row>
     <row r="34">
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5394791234243426</v>
+        <v>0.5394791234243425</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3857011247696835</v>
+        <v>0.3857011247696834</v>
       </c>
       <c r="D35" t="n">
         <v>0.1537779986546591</v>
@@ -2815,10 +2815,10 @@
         <v>0.4344379796487708</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4334339392606038</v>
+        <v>0.4334339392606036</v>
       </c>
       <c r="D38" t="n">
-        <v>0.001004040388167093</v>
+        <v>0.001004040388167204</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5569933730109208</v>
+        <v>0.5569933730109212</v>
       </c>
     </row>
     <row r="39">
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4653345520848203</v>
+        <v>0.4653345520848202</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4840879159829741</v>
+        <v>0.4840879159829742</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0187533638981538</v>
+        <v>-0.01875336389815396</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4699270902660452</v>
+        <v>0.4699270902660445</v>
       </c>
     </row>
     <row r="40">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6175455689522186</v>
+        <v>0.6175455689522185</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3789088878499817</v>
+        <v>0.3789088878499818</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2386366811022368</v>
+        <v>0.2386366811022366</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4177957142027762</v>
+        <v>0.4177957142027764</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0002558880407978982</v>
+        <v>0.0002558880407971643</v>
       </c>
     </row>
     <row r="43">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3383392939535172</v>
+        <v>0.3383392939535171</v>
       </c>
       <c r="C43" t="n">
         <v>0.5106782077019681</v>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.2068886854809436</v>
+        <v>-0.2068886854809439</v>
       </c>
     </row>
     <row r="44">
@@ -3175,10 +3175,10 @@
         <v>0.6041620014064532</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3523044639392301</v>
+        <v>0.35230446393923</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2518575374672231</v>
+        <v>0.2518575374672232</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
         <v>0.2921192787540448</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4188101764003092</v>
+        <v>0.4188101764003093</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462645</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.00572850172910837</v>
+        <v>-0.005728501729108615</v>
       </c>
     </row>
     <row r="46">
@@ -3355,10 +3355,10 @@
         <v>0.4809391108788849</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5016886059394928</v>
+        <v>0.5016886059394927</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060786</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4611306047729372</v>
+        <v>0.4611306047729377</v>
       </c>
     </row>
     <row r="48">
@@ -3415,10 +3415,10 @@
         <v>0.2314292087413117</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5043859448095896</v>
+        <v>0.5043859448095898</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.272956736068278</v>
+        <v>-0.2729567360682781</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.6502880126555675</v>
+        <v>-0.6502880126555679</v>
       </c>
     </row>
     <row r="49">
@@ -3595,7 +3595,7 @@
         <v>0.1845688251925361</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6485514885399383</v>
+        <v>0.6485514885399384</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4639826633474022</v>
@@ -3642,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>-1.492094818603322</v>
+        <v>-1.492094818603323</v>
       </c>
     </row>
     <row r="52">
@@ -3655,10 +3655,10 @@
         <v>0.2193986212219031</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5675900717151439</v>
+        <v>0.5675900717151438</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3481914504932407</v>
+        <v>-0.3481914504932406</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.9818298904967258</v>
+        <v>-0.9818298904967252</v>
       </c>
     </row>
     <row r="53">

--- a/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
+++ b/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3887806899776128</v>
+        <v>0.3887806899776127</v>
       </c>
     </row>
     <row r="13">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2738711846265848</v>
+        <v>0.2738711846265844</v>
       </c>
     </row>
   </sheetData>
@@ -655,10 +655,10 @@
         <v>0.6741225709545156</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3705533249609646</v>
+        <v>0.3705533249609647</v>
       </c>
       <c r="D2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935509</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>0.4023740554348589</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09053496729843552</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1536022691023414</v>
+        <v>0.1536022691023411</v>
       </c>
     </row>
     <row r="4">
@@ -775,10 +775,10 @@
         <v>0.5218386559860035</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5224770600152169</v>
+        <v>0.522477060015217</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0006384040292133353</v>
+        <v>-0.0006384040292134463</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5497555026933409</v>
+        <v>0.5497555026933404</v>
       </c>
     </row>
     <row r="5">
@@ -838,7 +838,7 @@
         <v>0.3376764996165211</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3490853798274803</v>
+        <v>0.3490853798274802</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
         <v>0.2972134155204859</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5512673902348847</v>
+        <v>0.5512673902348848</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2540539747143988</v>
+        <v>-0.2540539747143989</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.566987942421381</v>
+        <v>-0.5669879424213812</v>
       </c>
     </row>
     <row r="7">
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.019099448631347</v>
+        <v>1.019099448631348</v>
       </c>
     </row>
     <row r="11">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1869441246967854</v>
+        <v>0.1869441246967853</v>
       </c>
       <c r="C11" t="n">
-        <v>0.549050545884553</v>
+        <v>0.5490505458845529</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3621064211877677</v>
+        <v>-0.3621064211877676</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.043149928054248</v>
+        <v>-1.043149928054247</v>
       </c>
     </row>
     <row r="12">
@@ -1255,10 +1255,10 @@
         <v>0.250863755195081</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6293909101742613</v>
+        <v>0.6293909101742614</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3785271549791803</v>
+        <v>-0.3785271549791804</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
         <v>0.1716451268055921</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6729153871303859</v>
+        <v>0.6729153871303858</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247937</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         <v>0.2426910923322111</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6427190948063813</v>
+        <v>0.6427190948063815</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741704</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.210261511669543</v>
+        <v>-1.210261511669544</v>
       </c>
     </row>
     <row r="15">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3816235236497591</v>
+        <v>0.3816235236497592</v>
       </c>
       <c r="C15" t="n">
         <v>0.5485467523459439</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961847</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1830230217943294</v>
+        <v>-0.1830230217943291</v>
       </c>
     </row>
     <row r="16">
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2145524253023634</v>
+        <v>0.2145524253023635</v>
       </c>
       <c r="C17" t="n">
-        <v>0.600112064461128</v>
+        <v>0.6001120644611281</v>
       </c>
       <c r="D17" t="n">
         <v>-0.3855596391587646</v>
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4296518046208666</v>
+        <v>0.4296518046208667</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4945453559326177</v>
+        <v>0.4945453559326176</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06489355131175117</v>
+        <v>-0.06489355131175095</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2665980220829752</v>
+        <v>0.2665980220829762</v>
       </c>
     </row>
     <row r="19">
@@ -1675,10 +1675,10 @@
         <v>0.5237521220113416</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4697918671910091</v>
+        <v>0.4697918671910092</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05396025482033245</v>
+        <v>0.0539602548203324</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7903590860383859</v>
+        <v>0.7903590860383856</v>
       </c>
     </row>
     <row r="20">
@@ -1795,10 +1795,10 @@
         <v>0.7118486478275275</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4260034620050296</v>
+        <v>0.4260034620050295</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2858451858224979</v>
+        <v>0.285845185822498</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         <v>0.3010798522307473</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4999927429285567</v>
+        <v>0.4999927429285568</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3239940175984092</v>
+        <v>-0.3239940175984097</v>
       </c>
     </row>
     <row r="23">
@@ -1918,7 +1918,7 @@
         <v>0.4105420803197389</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1915672065927821</v>
+        <v>0.191567206592782</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2175554342042255</v>
+        <v>0.2175554342042256</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5970724973798153</v>
+        <v>0.5970724973798152</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3795170631755898</v>
+        <v>-0.3795170631755896</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.119874575488377</v>
+        <v>-1.119874575488376</v>
       </c>
     </row>
     <row r="25">
@@ -2155,10 +2155,10 @@
         <v>0.1922848927634011</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5332163798977593</v>
+        <v>0.5332163798977594</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3409314871343582</v>
+        <v>-0.3409314871343583</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.9498369215134701</v>
+        <v>-0.9498369215134705</v>
       </c>
     </row>
     <row r="28">
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3727681504267595</v>
+        <v>0.3727681504267594</v>
       </c>
       <c r="C29" t="n">
         <v>0.5189573803652675</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.146189229938508</v>
+        <v>-0.1461892299385081</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.0916531144873437</v>
+        <v>-0.09165311448734419</v>
       </c>
     </row>
     <row r="30">
@@ -2395,10 +2395,10 @@
         <v>0.2726179454172194</v>
       </c>
       <c r="C31" t="n">
-        <v>0.562389807099402</v>
+        <v>0.5623898070994021</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2897718616821826</v>
+        <v>-0.2897718616821827</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.7243883580184676</v>
+        <v>-0.724388358018468</v>
       </c>
     </row>
     <row r="32">
@@ -2455,10 +2455,10 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4830115777026099</v>
+        <v>0.4830115777026097</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.06676696903508088</v>
+        <v>-0.06676696903508014</v>
       </c>
     </row>
     <row r="33">
@@ -2515,10 +2515,10 @@
         <v>0.3328760832679651</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4307152111273059</v>
+        <v>0.4307152111273058</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934068</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1214145333353489</v>
+        <v>0.1214145333353491</v>
       </c>
     </row>
     <row r="34">
@@ -2635,10 +2635,10 @@
         <v>0.5394791234243425</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3857011247696834</v>
+        <v>0.3857011247696835</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1537779986546591</v>
+        <v>0.153777998654659</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         <v>0.2703323498637417</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5056838147445358</v>
+        <v>0.5056838147445357</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2353514648807942</v>
+        <v>-0.2353514648807941</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.4845703340344918</v>
+        <v>-0.4845703340344913</v>
       </c>
     </row>
     <row r="38">
@@ -2815,10 +2815,10 @@
         <v>0.4344379796487708</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4334339392606036</v>
+        <v>0.4334339392606038</v>
       </c>
       <c r="D38" t="n">
-        <v>0.001004040388167204</v>
+        <v>0.001004040388167038</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5569933730109212</v>
+        <v>0.5569933730109206</v>
       </c>
     </row>
     <row r="39">
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4653345520848202</v>
+        <v>0.4653345520848203</v>
       </c>
       <c r="C39" t="n">
         <v>0.4840879159829742</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.01875336389815396</v>
+        <v>-0.01875336389815391</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4699270902660445</v>
+        <v>0.4699270902660447</v>
       </c>
     </row>
     <row r="40">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6175455689522185</v>
+        <v>0.6175455689522186</v>
       </c>
       <c r="C40" t="n">
         <v>0.3789088878499818</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2386366811022366</v>
+        <v>0.2386366811022367</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>0.3852882355996786</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4177957142027764</v>
+        <v>0.4177957142027763</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0002558880407971643</v>
+        <v>0.0002558880407976535</v>
       </c>
     </row>
     <row r="43">
@@ -3175,10 +3175,10 @@
         <v>0.6041620014064532</v>
       </c>
       <c r="C44" t="n">
-        <v>0.35230446393923</v>
+        <v>0.3523044639392302</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2518575374672232</v>
+        <v>0.251857537467223</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
         <v>0.2921192787540448</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4188101764003093</v>
+        <v>0.4188101764003092</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1266908976462645</v>
+        <v>-0.1266908976462644</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.005728501729108615</v>
+        <v>-0.00572850172910837</v>
       </c>
     </row>
     <row r="46">
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4438010204861124</v>
+        <v>0.4438010204861125</v>
       </c>
       <c r="C46" t="n">
         <v>0.6094110466377607</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1656100261516483</v>
+        <v>-0.1656100261516482</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.1772360437891739</v>
+        <v>-0.1772360437891734</v>
       </c>
     </row>
     <row r="47">
@@ -3355,10 +3355,10 @@
         <v>0.4809391108788849</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5016886059394927</v>
+        <v>0.5016886059394928</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.02074949506060786</v>
+        <v>-0.02074949506060797</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4611306047729377</v>
+        <v>0.4611306047729372</v>
       </c>
     </row>
     <row r="48">
@@ -3475,10 +3475,10 @@
         <v>0.1990497928951852</v>
       </c>
       <c r="C49" t="n">
-        <v>0.652157489144949</v>
+        <v>0.6521574891449489</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.444171369427372</v>
+        <v>-1.444171369427371</v>
       </c>
     </row>
     <row r="50">
@@ -3655,10 +3655,10 @@
         <v>0.2193986212219031</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5675900717151438</v>
+        <v>0.5675900717151439</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3481914504932406</v>
+        <v>-0.3481914504932407</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.9818298904967252</v>
+        <v>-0.9818298904967258</v>
       </c>
     </row>
     <row r="53">

--- a/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
+++ b/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1558996280450781</v>
+        <v>-0.1558996280450782</v>
       </c>
     </row>
     <row r="6">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7128634150487455</v>
+        <v>0.7128634150487454</v>
       </c>
     </row>
     <row r="12">
@@ -655,10 +655,10 @@
         <v>0.6741225709545156</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3705533249609647</v>
+        <v>0.3705533249609646</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3035692459935509</v>
+        <v>0.303569245993551</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         <v>0.3118390881364234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4023740554348589</v>
+        <v>0.402374055434859</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843569</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1536022691023411</v>
+        <v>0.1536022691023406</v>
       </c>
     </row>
     <row r="4">
@@ -835,10 +835,10 @@
         <v>0.6867618794440014</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3376764996165211</v>
+        <v>0.337676499616521</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3490853798274802</v>
+        <v>0.3490853798274803</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
         <v>0.2972134155204859</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5512673902348848</v>
+        <v>0.5512673902348847</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2540539747143989</v>
+        <v>-0.2540539747143988</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5669879424213812</v>
+        <v>-0.5669879424213806</v>
       </c>
     </row>
     <row r="7">
@@ -1015,10 +1015,10 @@
         <v>0.5951237281573063</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4041932886603294</v>
+        <v>0.4041932886603293</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1909304394969769</v>
+        <v>0.190930439496977</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5748115671389329</v>
+        <v>0.5748115671389328</v>
       </c>
       <c r="C10" t="n">
         <v>0.4689446995877983</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1058668675511346</v>
+        <v>0.1058668675511344</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.019099448631348</v>
+        <v>1.019099448631347</v>
       </c>
     </row>
     <row r="11">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1869441246967853</v>
+        <v>0.1869441246967854</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5490505458845529</v>
+        <v>0.549050545884553</v>
       </c>
       <c r="D11" t="n">
         <v>-0.3621064211877676</v>
@@ -1255,10 +1255,10 @@
         <v>0.250863755195081</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6293909101742614</v>
+        <v>0.6293909101742613</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3785271549791804</v>
+        <v>-0.3785271549791803</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
         <v>0.1716451268055921</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6729153871303858</v>
+        <v>0.6729153871303859</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5012702603247937</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         <v>0.2426910923322111</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6427190948063815</v>
+        <v>0.6427190948063813</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4000280024741704</v>
+        <v>-0.4000280024741703</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.210261511669544</v>
+        <v>-1.210261511669543</v>
       </c>
     </row>
     <row r="15">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3816235236497592</v>
+        <v>0.381623523649759</v>
       </c>
       <c r="C15" t="n">
         <v>0.5485467523459439</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1669232286961847</v>
+        <v>-0.1669232286961848</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1830230217943291</v>
+        <v>-0.1830230217943296</v>
       </c>
     </row>
     <row r="16">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2828138579726733</v>
+        <v>0.2828138579726732</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4976624590930342</v>
+        <v>0.4976624590930341</v>
       </c>
       <c r="D16" t="n">
         <v>-0.2148486011203609</v>
@@ -1542,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3942189848706004</v>
+        <v>-0.3942189848706001</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4296518046208667</v>
+        <v>0.4296518046208666</v>
       </c>
       <c r="C18" t="n">
         <v>0.4945453559326176</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06489355131175095</v>
+        <v>-0.06489355131175106</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2665980220829762</v>
+        <v>0.2665980220829757</v>
       </c>
     </row>
     <row r="19">
@@ -1675,10 +1675,10 @@
         <v>0.5237521220113416</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4697918671910092</v>
+        <v>0.4697918671910091</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0539602548203324</v>
+        <v>0.05396025482033245</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7903590860383856</v>
+        <v>0.7903590860383859</v>
       </c>
     </row>
     <row r="20">
@@ -1735,10 +1735,10 @@
         <v>0.3693076732017413</v>
       </c>
       <c r="C20" t="n">
-        <v>0.515004568135498</v>
+        <v>0.5150045681354979</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1456968949337566</v>
+        <v>-0.1456968949337565</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08948350869765193</v>
+        <v>-0.08948350869765143</v>
       </c>
     </row>
     <row r="21">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7118486478275275</v>
+        <v>0.7118486478275274</v>
       </c>
       <c r="C21" t="n">
         <v>0.4260034620050295</v>
@@ -1855,10 +1855,10 @@
         <v>0.3010798522307473</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4999927429285568</v>
+        <v>0.4999927429285567</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1989128906978095</v>
+        <v>-0.1989128906978094</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3239940175984097</v>
+        <v>-0.3239940175984092</v>
       </c>
     </row>
     <row r="23">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.602109286912521</v>
+        <v>0.6021092869125209</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4105420803197389</v>
+        <v>0.410542080319739</v>
       </c>
       <c r="D23" t="n">
-        <v>0.191567206592782</v>
+        <v>0.1915672065927819</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.396760898597113</v>
+        <v>1.396760898597112</v>
       </c>
     </row>
     <row r="24">
@@ -1975,10 +1975,10 @@
         <v>0.2175554342042256</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5970724973798152</v>
+        <v>0.5970724973798153</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3795170631755896</v>
+        <v>-0.3795170631755897</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.547386166559502</v>
+        <v>0.5473861665595021</v>
       </c>
       <c r="C25" t="n">
         <v>0.4276290460083051</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1197571205511969</v>
+        <v>0.119757120551197</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         <v>0.1922848927634011</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5332163798977594</v>
+        <v>0.5332163798977593</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3409314871343583</v>
+        <v>-0.3409314871343582</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.9498369215134705</v>
+        <v>-0.9498369215134701</v>
       </c>
     </row>
     <row r="28">
@@ -2275,10 +2275,10 @@
         <v>0.3727681504267594</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5189573803652675</v>
+        <v>0.5189573803652676</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1461892299385081</v>
+        <v>-0.1461892299385082</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.09165311448734419</v>
+        <v>-0.09165311448734444</v>
       </c>
     </row>
     <row r="30">
@@ -2335,10 +2335,10 @@
         <v>0.2292739130871298</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4250474383301707</v>
+        <v>0.4250474383301708</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1957735252430409</v>
+        <v>-0.195773525243041</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.3101595646326616</v>
+        <v>-0.3101595646326621</v>
       </c>
     </row>
     <row r="31">
@@ -2455,10 +2455,10 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4830115777026097</v>
+        <v>0.4830115777026099</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.06676696903508014</v>
+        <v>-0.06676696903508111</v>
       </c>
     </row>
     <row r="33">
@@ -2518,7 +2518,7 @@
         <v>0.4307152111273058</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.09783912785934068</v>
+        <v>-0.09783912785934062</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1214145333353491</v>
+        <v>0.1214145333353493</v>
       </c>
     </row>
     <row r="34">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5394791234243425</v>
+        <v>0.5394791234243426</v>
       </c>
       <c r="C35" t="n">
         <v>0.3857011247696835</v>
@@ -2755,10 +2755,10 @@
         <v>0.2703323498637417</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5056838147445357</v>
+        <v>0.5056838147445358</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2353514648807941</v>
+        <v>-0.2353514648807942</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.4845703340344913</v>
+        <v>-0.4845703340344918</v>
       </c>
     </row>
     <row r="38">
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4653345520848203</v>
+        <v>0.4653345520848202</v>
       </c>
       <c r="C39" t="n">
         <v>0.4840879159829742</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.01875336389815391</v>
+        <v>-0.01875336389815396</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4699270902660447</v>
+        <v>0.4699270902660445</v>
       </c>
     </row>
     <row r="40">
@@ -2998,7 +2998,7 @@
         <v>0.3852882355996786</v>
       </c>
       <c r="D41" t="n">
-        <v>0.176800648574842</v>
+        <v>0.1768006485748421</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4177957142027763</v>
+        <v>0.4177957142027764</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0002558880407976535</v>
+        <v>0.0002558880407971643</v>
       </c>
     </row>
     <row r="43">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6041620014064532</v>
+        <v>0.6041620014064533</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3523044639392302</v>
+        <v>0.35230446393923</v>
       </c>
       <c r="D44" t="n">
-        <v>0.251857537467223</v>
+        <v>0.2518575374672233</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.662446355989435</v>
+        <v>1.662446355989436</v>
       </c>
     </row>
     <row r="45">
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4438010204861125</v>
+        <v>0.4438010204861124</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6094110466377607</v>
+        <v>0.6094110466377606</v>
       </c>
       <c r="D46" t="n">
         <v>-0.1656100261516482</v>
@@ -3415,10 +3415,10 @@
         <v>0.2314292087413117</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5043859448095898</v>
+        <v>0.5043859448095896</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.6502880126555679</v>
+        <v>-0.6502880126555675</v>
       </c>
     </row>
     <row r="49">
@@ -3475,10 +3475,10 @@
         <v>0.1990497928951852</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6521574891449489</v>
+        <v>0.652157489144949</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4531076962497637</v>
+        <v>-0.4531076962497638</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.444171369427371</v>
+        <v>-1.444171369427372</v>
       </c>
     </row>
     <row r="50">
@@ -3595,7 +3595,7 @@
         <v>0.1845688251925361</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6485514885399384</v>
+        <v>0.6485514885399383</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4639826633474022</v>
@@ -3642,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>-1.492094818603323</v>
+        <v>-1.492094818603322</v>
       </c>
     </row>
     <row r="52">

--- a/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
+++ b/results/GSE186332/selinexor_recurrence_score_clinical_association.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1612322114446527</v>
+        <v>-0.1612322114446526</v>
       </c>
     </row>
     <row r="5">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7128634150487454</v>
+        <v>0.7128634150487453</v>
       </c>
     </row>
     <row r="12">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3887806899776127</v>
+        <v>0.3887806899776126</v>
       </c>
     </row>
     <row r="13">
@@ -655,10 +655,10 @@
         <v>0.6741225709545156</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3705533249609646</v>
+        <v>0.3705533249609645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935511</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         <v>0.3118390881364234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.402374055434859</v>
+        <v>0.4023740554348589</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1536022691023406</v>
+        <v>0.1536022691023413</v>
       </c>
     </row>
     <row r="4">
@@ -775,10 +775,10 @@
         <v>0.5218386559860035</v>
       </c>
       <c r="C4" t="n">
-        <v>0.522477060015217</v>
+        <v>0.5224770600152169</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5497555026933404</v>
+        <v>0.5497555026933408</v>
       </c>
     </row>
     <row r="5">
@@ -835,7 +835,7 @@
         <v>0.6867618794440014</v>
       </c>
       <c r="C5" t="n">
-        <v>0.337676499616521</v>
+        <v>0.3376764996165211</v>
       </c>
       <c r="D5" t="n">
         <v>0.3490853798274803</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5669879424213806</v>
+        <v>-0.5669879424213808</v>
       </c>
     </row>
     <row r="7">
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8826594532747009</v>
+        <v>-0.882659453274701</v>
       </c>
     </row>
     <row r="8">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5951237281573063</v>
+        <v>0.5951237281573062</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4041932886603293</v>
+        <v>0.4041932886603294</v>
       </c>
       <c r="D8" t="n">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969768</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.393954814194397</v>
+        <v>1.393954814194396</v>
       </c>
     </row>
     <row r="9">
@@ -1075,10 +1075,10 @@
         <v>0.4417500520544824</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4663157299697189</v>
+        <v>0.4663157299697188</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02456567791523645</v>
+        <v>-0.02456567791523639</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.444313575035014</v>
+        <v>0.4443135750350141</v>
       </c>
     </row>
     <row r="10">
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5748115671389328</v>
+        <v>0.5748115671389329</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4689446995877983</v>
+        <v>0.4689446995877984</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1058668675511344</v>
+        <v>0.1058668675511345</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1869441246967854</v>
+        <v>0.1869441246967853</v>
       </c>
       <c r="C11" t="n">
         <v>0.549050545884553</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3621064211877676</v>
+        <v>-0.3621064211877677</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.043149928054247</v>
+        <v>-1.043149928054248</v>
       </c>
     </row>
     <row r="12">
@@ -1315,10 +1315,10 @@
         <v>0.1716451268055921</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6729153871303859</v>
+        <v>0.6729153871303858</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247936</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.656412580909693</v>
+        <v>-1.656412580909692</v>
       </c>
     </row>
     <row r="14">
@@ -1375,10 +1375,10 @@
         <v>0.2426910923322111</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6427190948063813</v>
+        <v>0.6427190948063812</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4000280024741703</v>
+        <v>-0.4000280024741701</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1830230217943296</v>
+        <v>-0.1830230217943297</v>
       </c>
     </row>
     <row r="16">
@@ -1495,10 +1495,10 @@
         <v>0.2828138579726732</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4976624590930341</v>
+        <v>0.4976624590930342</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2148486011203609</v>
+        <v>-0.214848601120361</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3942189848706001</v>
+        <v>-0.3942189848706007</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4296518046208666</v>
+        <v>0.4296518046208667</v>
       </c>
       <c r="C18" t="n">
         <v>0.4945453559326176</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06489355131175106</v>
+        <v>-0.06489355131175095</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2665980220829757</v>
+        <v>0.2665980220829761</v>
       </c>
     </row>
     <row r="19">
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5237521220113416</v>
+        <v>0.5237521220113415</v>
       </c>
       <c r="C19" t="n">
         <v>0.4697918671910091</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05396025482033245</v>
+        <v>0.05396025482033234</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7903590860383859</v>
+        <v>0.7903590860383852</v>
       </c>
     </row>
     <row r="20">
@@ -1735,10 +1735,10 @@
         <v>0.3693076732017413</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5150045681354979</v>
+        <v>0.515004568135498</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1456968949337565</v>
+        <v>-0.1456968949337566</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08948350869765143</v>
+        <v>-0.08948350869765204</v>
       </c>
     </row>
     <row r="21">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7118486478275274</v>
+        <v>0.7118486478275275</v>
       </c>
       <c r="C21" t="n">
         <v>0.4260034620050295</v>
       </c>
       <c r="D21" t="n">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224981</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         <v>0.3010798522307473</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4999927429285567</v>
+        <v>0.4999927429285569</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1989128906978094</v>
+        <v>-0.1989128906978095</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3239940175984092</v>
+        <v>-0.3239940175984101</v>
       </c>
     </row>
     <row r="23">
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6021092869125209</v>
+        <v>0.602109286912521</v>
       </c>
       <c r="C23" t="n">
-        <v>0.410542080319739</v>
+        <v>0.4105420803197389</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1915672065927819</v>
+        <v>0.191567206592782</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.396760898597112</v>
+        <v>1.396760898597113</v>
       </c>
     </row>
     <row r="24">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2175554342042256</v>
+        <v>0.2175554342042255</v>
       </c>
       <c r="C24" t="n">
         <v>0.5970724973798153</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3795170631755897</v>
+        <v>-0.3795170631755898</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.119874575488376</v>
+        <v>-1.119874575488377</v>
       </c>
     </row>
     <row r="25">
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.8857822140406025</v>
+        <v>-0.8857822140406024</v>
       </c>
     </row>
     <row r="27">
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.9498369215134701</v>
+        <v>-0.9498369215134702</v>
       </c>
     </row>
     <row r="28">
@@ -2275,10 +2275,10 @@
         <v>0.3727681504267594</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5189573803652676</v>
+        <v>0.5189573803652675</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1461892299385082</v>
+        <v>-0.1461892299385081</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.09165311448734444</v>
+        <v>-0.09165311448734406</v>
       </c>
     </row>
     <row r="30">
@@ -2382,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.3101595646326621</v>
+        <v>-0.3101595646326622</v>
       </c>
     </row>
     <row r="31">
@@ -2395,10 +2395,10 @@
         <v>0.2726179454172194</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5623898070994021</v>
+        <v>0.5623898070994019</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2897718616821827</v>
+        <v>-0.2897718616821825</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.724388358018468</v>
+        <v>-0.7243883580184671</v>
       </c>
     </row>
     <row r="32">
@@ -2455,10 +2455,10 @@
         <v>0.3424696043291868</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4830115777026099</v>
+        <v>0.4830115777026098</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.06676696903508111</v>
+        <v>-0.0667669690350805</v>
       </c>
     </row>
     <row r="33">
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1214145333353493</v>
+        <v>0.1214145333353492</v>
       </c>
     </row>
     <row r="34">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5394791234243426</v>
+        <v>0.5394791234243425</v>
       </c>
       <c r="C35" t="n">
         <v>0.3857011247696835</v>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.230232653521748</v>
+        <v>1.230232653521747</v>
       </c>
     </row>
     <row r="36">
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.7129966652452815</v>
+        <v>-0.7129966652452816</v>
       </c>
     </row>
     <row r="37">
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.4845703340344918</v>
+        <v>-0.484570334034492</v>
       </c>
     </row>
     <row r="38">
@@ -2862,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5569933730109206</v>
+        <v>0.5569933730109203</v>
       </c>
     </row>
     <row r="39">
@@ -2922,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4699270902660445</v>
+        <v>0.4699270902660443</v>
       </c>
     </row>
     <row r="40">
@@ -2935,7 +2935,7 @@
         <v>0.6175455689522186</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3789088878499818</v>
+        <v>0.3789088878499819</v>
       </c>
       <c r="D40" t="n">
         <v>0.2386366811022367</v>
@@ -2998,7 +2998,7 @@
         <v>0.3852882355996786</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1768006485748421</v>
+        <v>0.176800648574842</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         <v>0.2924628165119874</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4177957142027764</v>
+        <v>0.4177957142027763</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.0002558880407971643</v>
+        <v>0.0002558880407975312</v>
       </c>
     </row>
     <row r="43">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3383392939535171</v>
+        <v>0.3383392939535172</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5106782077019681</v>
+        <v>0.510678207701968</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.172338913748451</v>
+        <v>-0.1723389137484508</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.2068886854809439</v>
+        <v>-0.2068886854809432</v>
       </c>
     </row>
     <row r="44">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6041620014064533</v>
+        <v>0.6041620014064532</v>
       </c>
       <c r="C44" t="n">
-        <v>0.35230446393923</v>
+        <v>0.3523044639392302</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2518575374672233</v>
+        <v>0.251857537467223</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.662446355989436</v>
+        <v>1.662446355989434</v>
       </c>
     </row>
     <row r="45">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2921192787540448</v>
+        <v>0.2921192787540449</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4188101764003092</v>
+        <v>0.4188101764003091</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1266908976462644</v>
+        <v>-0.1266908976462642</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.00572850172910837</v>
+        <v>-0.005728501729107759</v>
       </c>
     </row>
     <row r="46">
@@ -3295,10 +3295,10 @@
         <v>0.4438010204861124</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6094110466377606</v>
+        <v>0.6094110466377607</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1656100261516482</v>
+        <v>-0.1656100261516483</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.1772360437891734</v>
+        <v>-0.177236043789174</v>
       </c>
     </row>
     <row r="47">
@@ -3355,10 +3355,10 @@
         <v>0.4809391108788849</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5016886059394928</v>
+        <v>0.5016886059394929</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.02074949506060797</v>
+        <v>-0.02074949506060808</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4611306047729372</v>
+        <v>0.4611306047729365</v>
       </c>
     </row>
     <row r="48">
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.6502880126555675</v>
+        <v>-0.6502880126555676</v>
       </c>
     </row>
     <row r="49">
@@ -3475,10 +3475,10 @@
         <v>0.1990497928951852</v>
       </c>
       <c r="C49" t="n">
-        <v>0.652157489144949</v>
+        <v>0.6521574891449489</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4531076962497638</v>
+        <v>-0.4531076962497637</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.6321605150517657</v>
+        <v>-0.6321605150517658</v>
       </c>
     </row>
     <row r="51">
@@ -3595,10 +3595,10 @@
         <v>0.1845688251925361</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6485514885399383</v>
+        <v>0.6485514885399384</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4639826633474022</v>
+        <v>-0.4639826633474023</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>-1.492094818603322</v>
+        <v>-1.492094818603323</v>
       </c>
     </row>
     <row r="52">
@@ -3702,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.9818298904967258</v>
+        <v>-0.9818298904967259</v>
       </c>
     </row>
     <row r="53">
@@ -3715,10 +3715,10 @@
         <v>0.2019181367419962</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5318470851017671</v>
+        <v>0.531847085101767</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.329928948359771</v>
+        <v>-0.3299289483597709</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.9013512936456988</v>
+        <v>-0.9013512936456984</v>
       </c>
     </row>
   </sheetData>
